--- a/Dataset_Augmented.xlsx
+++ b/Dataset_Augmented.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 6\Visualisasi Informasi\Syntax\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 6\Visualisasi Informasi\Random Forest Digital Twin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846B74BB-C033-45F3-9039-11D452B3C0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410EAFA2-91D7-47E6-992C-EF64C885B704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="91">
   <si>
     <t>Nama_Titik</t>
   </si>
@@ -349,11 +349,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -6604,6 +6605,61 @@
         <v>75</v>
       </c>
     </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D146" s="2">
+        <f>AVERAGE(D2:D145)</f>
+        <v>69.865555555555574</v>
+      </c>
+      <c r="F146" s="2">
+        <f>AVERAGE(F2:F145)</f>
+        <v>42.881458333333313</v>
+      </c>
+      <c r="H146" s="2">
+        <f>AVERAGE(H2:H145)</f>
+        <v>79.198055555555513</v>
+      </c>
+      <c r="J146" s="2">
+        <f>AVERAGE(J2:J145)</f>
+        <v>6.5504166666666688</v>
+      </c>
+      <c r="K146" s="2">
+        <f>AVERAGE(K2:K145)</f>
+        <v>71.630972222222255</v>
+      </c>
+      <c r="L146" s="2">
+        <f>AVERAGE(L2:L145)</f>
+        <v>23.147916666666678</v>
+      </c>
+      <c r="M146" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D148" s="2">
+        <f>_xlfn.STDEV.S(D2:D145)</f>
+        <v>19.198954363200308</v>
+      </c>
+      <c r="F148" s="2">
+        <f>_xlfn.STDEV.S(F2:F145)</f>
+        <v>7.4265885935679341</v>
+      </c>
+      <c r="H148" s="2">
+        <f>_xlfn.STDEV.S(H2:H145)</f>
+        <v>13.608911019246463</v>
+      </c>
+      <c r="J148" s="2">
+        <f>_xlfn.STDEV.S(J2:J145)</f>
+        <v>0.7891651559443138</v>
+      </c>
+      <c r="K148" s="2">
+        <f t="shared" ref="K148:L148" si="0">_xlfn.STDEV.S(K2:K145)</f>
+        <v>6.0656523893406469</v>
+      </c>
+      <c r="L148" s="2">
+        <f t="shared" si="0"/>
+        <v>2.126650695769801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
